--- a/Smoke-tests/Smoke4 - Добавление товара в корзину способ2.xlsx
+++ b/Smoke-tests/Smoke4 - Добавление товара в корзину способ2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yaros\Documents\Smoke-tests\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C5641F08-6C66-4CC9-809F-EF4C671D7061}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0EFF3DA5-E5F9-45A7-970D-B556649F8186}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8490" yWindow="3285" windowWidth="23160" windowHeight="11685" xr2:uid="{60CBE097-ABDC-4BE2-8156-EB43CE3551D6}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" xr2:uid="{60CBE097-ABDC-4BE2-8156-EB43CE3551D6}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -85,40 +85,40 @@
 3) Открыт главный экран</t>
   </si>
   <si>
-    <t>Перейти в "Кабинет"</t>
-  </si>
-  <si>
-    <t>Нажать на "Корзина"</t>
-  </si>
-  <si>
     <t>Корзина пустая</t>
   </si>
   <si>
     <t>Осуществился переход на страницу "Мои заказы"</t>
   </si>
   <si>
-    <t>Нажать на "Нажмите здесь"</t>
-  </si>
-  <si>
     <t>Переход в каталог поставщика(B2B-кабинет компании, автоматически выбрана первая в списке)</t>
   </si>
   <si>
-    <t>Изменить количество первого товара на 1, нажав на "+"</t>
-  </si>
-  <si>
     <t>Количество товара = 1</t>
   </si>
   <si>
-    <t>Нажать на "В корзину предварительного заказа"</t>
-  </si>
-  <si>
     <t>Открылось уточняющее окно с вопросом о переходе в корзину.</t>
   </si>
   <si>
-    <t>Выбрать "Перейти в предварительный заказ"</t>
-  </si>
-  <si>
     <t>Осуществился переход в корзину(оформление заказа)</t>
+  </si>
+  <si>
+    <t>1) Перейти в "Кабинет"</t>
+  </si>
+  <si>
+    <t>2) Нажать на "Корзина"</t>
+  </si>
+  <si>
+    <t>3) Нажать на "Нажмите здесь"</t>
+  </si>
+  <si>
+    <t>4) Изменить количество первого товара на 1, нажав на "+"</t>
+  </si>
+  <si>
+    <t>5) Нажать на "В корзину предварительного заказа"</t>
+  </si>
+  <si>
+    <t>6) Выбрать "Перейти в предварительный заказ"</t>
   </si>
 </sst>
 </file>
@@ -686,11 +686,11 @@
         <v>14</v>
       </c>
       <c r="F2" s="6" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="G2" s="6"/>
       <c r="H2" s="6" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="I2" s="7" t="s">
         <v>11</v>
@@ -703,11 +703,11 @@
       <c r="D3" s="6"/>
       <c r="E3" s="6"/>
       <c r="F3" s="6" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="G3" s="11"/>
       <c r="H3" s="6" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="I3" s="7"/>
     </row>
@@ -718,11 +718,11 @@
       <c r="D4" s="6"/>
       <c r="E4" s="6"/>
       <c r="F4" s="6" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="G4" s="11"/>
       <c r="H4" s="6" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="I4" s="7"/>
     </row>
@@ -733,11 +733,11 @@
       <c r="D5" s="6"/>
       <c r="E5" s="6"/>
       <c r="F5" s="6" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="G5" s="6"/>
       <c r="H5" s="6" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="I5" s="7"/>
     </row>
@@ -748,11 +748,11 @@
       <c r="D6" s="6"/>
       <c r="E6" s="6"/>
       <c r="F6" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="G6" s="6"/>
       <c r="H6" s="6" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="I6" s="7"/>
     </row>
@@ -763,11 +763,11 @@
       <c r="D7" s="6"/>
       <c r="E7" s="6"/>
       <c r="F7" s="6" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G7" s="6"/>
       <c r="H7" s="6" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="I7" s="7"/>
     </row>
